--- a/budget/output/Сводный бюджет СПб2.xlsx
+++ b/budget/output/Сводный бюджет СПб2.xlsx
@@ -2657,35 +2657,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -4507,35 +4507,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -4907,35 +4907,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -4957,35 +4957,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -5357,35 +5357,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -5407,35 +5407,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -7752,35 +7752,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -9209,16 +9209,44 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
@@ -9810,35 +9838,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -10250,35 +10278,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -10300,35 +10328,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -10720,35 +10748,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -10770,35 +10798,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -13097,35 +13125,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -14556,18 +14584,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -15161,35 +15213,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -15601,35 +15653,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -15651,35 +15703,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -16071,35 +16123,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -16121,35 +16173,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -18458,35 +18510,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -19907,18 +19959,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -20512,35 +20588,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -20952,35 +21028,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -21002,35 +21078,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -21422,35 +21498,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -21472,35 +21548,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -23835,35 +23911,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -25294,18 +25370,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -25899,35 +25999,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -26339,35 +26439,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -26389,35 +26489,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -26809,35 +26909,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -26859,35 +26959,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>

--- a/budget/output/Сводный бюджет СПб2.xlsx
+++ b/budget/output/Сводный бюджет СПб2.xlsx
@@ -680,9 +680,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -707,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM('Астрид'!B5,'Курортный'!B5,'Новое Колпино'!B5,'Таллинский парк'!B5)</f>
+        <f>SUM(C5,D5,E5,F5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -730,9 +731,10 @@
         <f>SUM('Астрид'!G5,'Курортный'!G5,'Новое Колпино'!G5,'Таллинский парк'!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="7">
-        <f>SUM('Астрид'!H5,'Курортный'!H5,'Новое Колпино'!H5,'Таллинский парк'!H5)</f>
-        <v/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I5" s="7">
         <f>SUM('Астрид'!I5,'Курортный'!I5,'Новое Колпино'!I5,'Таллинский парк'!I5)</f>
@@ -780,9 +782,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -807,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM('Астрид'!B7,'Курортный'!B7,'Новое Колпино'!B7,'Таллинский парк'!B7)</f>
+        <f>SUM(C7,D7,E7,F7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -830,9 +833,10 @@
         <f>SUM('Астрид'!G7,'Курортный'!G7,'Новое Колпино'!G7,'Таллинский парк'!G7)</f>
         <v/>
       </c>
-      <c r="H7" s="7">
-        <f>SUM('Астрид'!H7,'Курортный'!H7,'Новое Колпино'!H7,'Таллинский парк'!H7)</f>
-        <v/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I7" s="7">
         <f>SUM('Астрид'!I7,'Курортный'!I7,'Новое Колпино'!I7,'Таллинский парк'!I7)</f>
@@ -857,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM('Астрид'!B8,'Курортный'!B8,'Новое Колпино'!B8,'Таллинский парк'!B8)</f>
+        <f>SUM(C8,D8,E8,F8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -880,9 +884,10 @@
         <f>SUM('Астрид'!G8,'Курортный'!G8,'Новое Колпино'!G8,'Таллинский парк'!G8)</f>
         <v/>
       </c>
-      <c r="H8" s="7">
-        <f>SUM('Астрид'!H8,'Курортный'!H8,'Новое Колпино'!H8,'Таллинский парк'!H8)</f>
-        <v/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I8" s="7">
         <f>SUM('Астрид'!I8,'Курортный'!I8,'Новое Колпино'!I8,'Таллинский парк'!I8)</f>
@@ -907,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM('Астрид'!B9,'Курортный'!B9,'Новое Колпино'!B9,'Таллинский парк'!B9)</f>
+        <f>SUM(C9,D9,E9,F9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -930,9 +935,10 @@
         <f>SUM('Астрид'!G9,'Курортный'!G9,'Новое Колпино'!G9,'Таллинский парк'!G9)</f>
         <v/>
       </c>
-      <c r="H9" s="7">
-        <f>SUM('Астрид'!H9,'Курортный'!H9,'Новое Колпино'!H9,'Таллинский парк'!H9)</f>
-        <v/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I9" s="7">
         <f>SUM('Астрид'!I9,'Курортный'!I9,'Новое Колпино'!I9,'Таллинский парк'!I9)</f>
@@ -980,9 +986,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -1007,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM('Астрид'!B11,'Курортный'!B11,'Новое Колпино'!B11,'Таллинский парк'!B11)</f>
+        <f>SUM(C11,D11,E11,F11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1030,9 +1037,10 @@
         <f>SUM('Астрид'!G11,'Курортный'!G11,'Новое Колпино'!G11,'Таллинский парк'!G11)</f>
         <v/>
       </c>
-      <c r="H11" s="7">
-        <f>SUM('Астрид'!H11,'Курортный'!H11,'Новое Колпино'!H11,'Таллинский парк'!H11)</f>
-        <v/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I11" s="7">
         <f>SUM('Астрид'!I11,'Курортный'!I11,'Новое Колпино'!I11,'Таллинский парк'!I11)</f>
@@ -1057,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM('Астрид'!B12,'Курортный'!B12,'Новое Колпино'!B12,'Таллинский парк'!B12)</f>
+        <f>SUM(C12,D12,E12,F12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1080,9 +1088,10 @@
         <f>SUM('Астрид'!G12,'Курортный'!G12,'Новое Колпино'!G12,'Таллинский парк'!G12)</f>
         <v/>
       </c>
-      <c r="H12" s="7">
-        <f>SUM('Астрид'!H12,'Курортный'!H12,'Новое Колпино'!H12,'Таллинский парк'!H12)</f>
-        <v/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I12" s="7">
         <f>SUM('Астрид'!I12,'Курортный'!I12,'Новое Колпино'!I12,'Таллинский парк'!I12)</f>
@@ -1130,9 +1139,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -1157,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM('Астрид'!B14,'Курортный'!B14,'Новое Колпино'!B14,'Таллинский парк'!B14)</f>
+        <f>SUM(C14,D14,E14,F14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1180,9 +1190,10 @@
         <f>SUM('Астрид'!G14,'Курортный'!G14,'Новое Колпино'!G14,'Таллинский парк'!G14)</f>
         <v/>
       </c>
-      <c r="H14" s="7">
-        <f>SUM('Астрид'!H14,'Курортный'!H14,'Новое Колпино'!H14,'Таллинский парк'!H14)</f>
-        <v/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I14" s="7">
         <f>SUM('Астрид'!I14,'Курортный'!I14,'Новое Колпино'!I14,'Таллинский парк'!I14)</f>
@@ -1207,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM('Астрид'!B15,'Курортный'!B15,'Новое Колпино'!B15,'Таллинский парк'!B15)</f>
+        <f>SUM(C15,D15,E15,F15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1230,9 +1241,10 @@
         <f>SUM('Астрид'!G15,'Курортный'!G15,'Новое Колпино'!G15,'Таллинский парк'!G15)</f>
         <v/>
       </c>
-      <c r="H15" s="7">
-        <f>SUM('Астрид'!H15,'Курортный'!H15,'Новое Колпино'!H15,'Таллинский парк'!H15)</f>
-        <v/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I15" s="7">
         <f>SUM('Астрид'!I15,'Курортный'!I15,'Новое Колпино'!I15,'Таллинский парк'!I15)</f>
@@ -1257,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM('Астрид'!B16,'Курортный'!B16,'Новое Колпино'!B16,'Таллинский парк'!B16)</f>
+        <f>SUM(C16,D16,E16,F16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1280,9 +1292,10 @@
         <f>SUM('Астрид'!G16,'Курортный'!G16,'Новое Колпино'!G16,'Таллинский парк'!G16)</f>
         <v/>
       </c>
-      <c r="H16" s="7">
-        <f>SUM('Астрид'!H16,'Курортный'!H16,'Новое Колпино'!H16,'Таллинский парк'!H16)</f>
-        <v/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I16" s="7">
         <f>SUM('Астрид'!I16,'Курортный'!I16,'Новое Колпино'!I16,'Таллинский парк'!I16)</f>
@@ -1307,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM('Астрид'!B17,'Курортный'!B17,'Новое Колпино'!B17,'Таллинский парк'!B17)</f>
+        <f>SUM(C17,D17,E17,F17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1330,9 +1343,10 @@
         <f>SUM('Астрид'!G17,'Курортный'!G17,'Новое Колпино'!G17,'Таллинский парк'!G17)</f>
         <v/>
       </c>
-      <c r="H17" s="7">
-        <f>SUM('Астрид'!H17,'Курортный'!H17,'Новое Колпино'!H17,'Таллинский парк'!H17)</f>
-        <v/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="7">
         <f>SUM('Астрид'!I17,'Курортный'!I17,'Новое Колпино'!I17,'Таллинский парк'!I17)</f>
@@ -1357,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM('Астрид'!B18,'Курортный'!B18,'Новое Колпино'!B18,'Таллинский парк'!B18)</f>
+        <f>SUM(C18,D18,E18,F18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1380,9 +1394,10 @@
         <f>SUM('Астрид'!G18,'Курортный'!G18,'Новое Колпино'!G18,'Таллинский парк'!G18)</f>
         <v/>
       </c>
-      <c r="H18" s="7">
-        <f>SUM('Астрид'!H18,'Курортный'!H18,'Новое Колпино'!H18,'Таллинский парк'!H18)</f>
-        <v/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="7">
         <f>SUM('Астрид'!I18,'Курортный'!I18,'Новое Колпино'!I18,'Таллинский парк'!I18)</f>
@@ -1407,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM('Астрид'!B19,'Курортный'!B19,'Новое Колпино'!B19,'Таллинский парк'!B19)</f>
+        <f>SUM(C19,D19,E19,F19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1430,9 +1445,10 @@
         <f>SUM('Астрид'!G19,'Курортный'!G19,'Новое Колпино'!G19,'Таллинский парк'!G19)</f>
         <v/>
       </c>
-      <c r="H19" s="7">
-        <f>SUM('Астрид'!H19,'Курортный'!H19,'Новое Колпино'!H19,'Таллинский парк'!H19)</f>
-        <v/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I19" s="7">
         <f>SUM('Астрид'!I19,'Курортный'!I19,'Новое Колпино'!I19,'Таллинский парк'!I19)</f>
@@ -1457,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM('Астрид'!B20,'Курортный'!B20,'Новое Колпино'!B20,'Таллинский парк'!B20)</f>
+        <f>SUM(C20,D20,E20,F20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1480,9 +1496,10 @@
         <f>SUM('Астрид'!G20,'Курортный'!G20,'Новое Колпино'!G20,'Таллинский парк'!G20)</f>
         <v/>
       </c>
-      <c r="H20" s="7">
-        <f>SUM('Астрид'!H20,'Курортный'!H20,'Новое Колпино'!H20,'Таллинский парк'!H20)</f>
-        <v/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="7">
         <f>SUM('Астрид'!I20,'Курортный'!I20,'Новое Колпино'!I20,'Таллинский парк'!I20)</f>
@@ -1507,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM('Астрид'!B21,'Курортный'!B21,'Новое Колпино'!B21,'Таллинский парк'!B21)</f>
+        <f>SUM(C21,D21,E21,F21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1530,9 +1547,10 @@
         <f>SUM('Астрид'!G21,'Курортный'!G21,'Новое Колпино'!G21,'Таллинский парк'!G21)</f>
         <v/>
       </c>
-      <c r="H21" s="7">
-        <f>SUM('Астрид'!H21,'Курортный'!H21,'Новое Колпино'!H21,'Таллинский парк'!H21)</f>
-        <v/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="7">
         <f>SUM('Астрид'!I21,'Курортный'!I21,'Новое Колпино'!I21,'Таллинский парк'!I21)</f>
@@ -1557,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM('Астрид'!B22,'Курортный'!B22,'Новое Колпино'!B22,'Таллинский парк'!B22)</f>
+        <f>SUM(C22,D22,E22,F22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1580,9 +1598,10 @@
         <f>SUM('Астрид'!G22,'Курортный'!G22,'Новое Колпино'!G22,'Таллинский парк'!G22)</f>
         <v/>
       </c>
-      <c r="H22" s="7">
-        <f>SUM('Астрид'!H22,'Курортный'!H22,'Новое Колпино'!H22,'Таллинский парк'!H22)</f>
-        <v/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I22" s="7">
         <f>SUM('Астрид'!I22,'Курортный'!I22,'Новое Колпино'!I22,'Таллинский парк'!I22)</f>
@@ -1607,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM('Астрид'!B23,'Курортный'!B23,'Новое Колпино'!B23,'Таллинский парк'!B23)</f>
+        <f>SUM(C23,D23,E23,F23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1630,9 +1649,10 @@
         <f>SUM('Астрид'!G23,'Курортный'!G23,'Новое Колпино'!G23,'Таллинский парк'!G23)</f>
         <v/>
       </c>
-      <c r="H23" s="7">
-        <f>SUM('Астрид'!H23,'Курортный'!H23,'Новое Колпино'!H23,'Таллинский парк'!H23)</f>
-        <v/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" s="7">
         <f>SUM('Астрид'!I23,'Курортный'!I23,'Новое Колпино'!I23,'Таллинский парк'!I23)</f>
@@ -1657,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM('Астрид'!B24,'Курортный'!B24,'Новое Колпино'!B24,'Таллинский парк'!B24)</f>
+        <f>SUM(C24,D24,E24,F24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1680,9 +1700,10 @@
         <f>SUM('Астрид'!G24,'Курортный'!G24,'Новое Колпино'!G24,'Таллинский парк'!G24)</f>
         <v/>
       </c>
-      <c r="H24" s="7">
-        <f>SUM('Астрид'!H24,'Курортный'!H24,'Новое Колпино'!H24,'Таллинский парк'!H24)</f>
-        <v/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I24" s="7">
         <f>SUM('Астрид'!I24,'Курортный'!I24,'Новое Колпино'!I24,'Таллинский парк'!I24)</f>
@@ -1707,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM('Астрид'!B25,'Курортный'!B25,'Новое Колпино'!B25,'Таллинский парк'!B25)</f>
+        <f>SUM(C25,D25,E25,F25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1730,9 +1751,10 @@
         <f>SUM('Астрид'!G25,'Курортный'!G25,'Новое Колпино'!G25,'Таллинский парк'!G25)</f>
         <v/>
       </c>
-      <c r="H25" s="7">
-        <f>SUM('Астрид'!H25,'Курортный'!H25,'Новое Колпино'!H25,'Таллинский парк'!H25)</f>
-        <v/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I25" s="7">
         <f>SUM('Астрид'!I25,'Курортный'!I25,'Новое Колпино'!I25,'Таллинский парк'!I25)</f>
@@ -1757,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM('Астрид'!B26,'Курортный'!B26,'Новое Колпино'!B26,'Таллинский парк'!B26)</f>
+        <f>SUM(C26,D26,E26,F26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1780,9 +1802,10 @@
         <f>SUM('Астрид'!G26,'Курортный'!G26,'Новое Колпино'!G26,'Таллинский парк'!G26)</f>
         <v/>
       </c>
-      <c r="H26" s="7">
-        <f>SUM('Астрид'!H26,'Курортный'!H26,'Новое Колпино'!H26,'Таллинский парк'!H26)</f>
-        <v/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I26" s="7">
         <f>SUM('Астрид'!I26,'Курортный'!I26,'Новое Колпино'!I26,'Таллинский парк'!I26)</f>
@@ -1807,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM('Астрид'!B27,'Курортный'!B27,'Новое Колпино'!B27,'Таллинский парк'!B27)</f>
+        <f>SUM(C27,D27,E27,F27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1830,9 +1853,10 @@
         <f>SUM('Астрид'!G27,'Курортный'!G27,'Новое Колпино'!G27,'Таллинский парк'!G27)</f>
         <v/>
       </c>
-      <c r="H27" s="7">
-        <f>SUM('Астрид'!H27,'Курортный'!H27,'Новое Колпино'!H27,'Таллинский парк'!H27)</f>
-        <v/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" s="7">
         <f>SUM('Астрид'!I27,'Курортный'!I27,'Новое Колпино'!I27,'Таллинский парк'!I27)</f>
@@ -1857,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM('Астрид'!B28,'Курортный'!B28,'Новое Колпино'!B28,'Таллинский парк'!B28)</f>
+        <f>SUM(C28,D28,E28,F28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1880,9 +1904,10 @@
         <f>SUM('Астрид'!G28,'Курортный'!G28,'Новое Колпино'!G28,'Таллинский парк'!G28)</f>
         <v/>
       </c>
-      <c r="H28" s="7">
-        <f>SUM('Астрид'!H28,'Курортный'!H28,'Новое Колпино'!H28,'Таллинский парк'!H28)</f>
-        <v/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" s="7">
         <f>SUM('Астрид'!I28,'Курортный'!I28,'Новое Колпино'!I28,'Таллинский парк'!I28)</f>
@@ -1907,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM('Астрид'!B29,'Курортный'!B29,'Новое Колпино'!B29,'Таллинский парк'!B29)</f>
+        <f>SUM(C29,D29,E29,F29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1930,9 +1955,10 @@
         <f>SUM('Астрид'!G29,'Курортный'!G29,'Новое Колпино'!G29,'Таллинский парк'!G29)</f>
         <v/>
       </c>
-      <c r="H29" s="7">
-        <f>SUM('Астрид'!H29,'Курортный'!H29,'Новое Колпино'!H29,'Таллинский парк'!H29)</f>
-        <v/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" s="7">
         <f>SUM('Астрид'!I29,'Курортный'!I29,'Новое Колпино'!I29,'Таллинский парк'!I29)</f>
@@ -1957,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM('Астрид'!B30,'Курортный'!B30,'Новое Колпино'!B30,'Таллинский парк'!B30)</f>
+        <f>SUM(C30,D30,E30,F30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -1980,9 +2006,10 @@
         <f>SUM('Астрид'!G30,'Курортный'!G30,'Новое Колпино'!G30,'Таллинский парк'!G30)</f>
         <v/>
       </c>
-      <c r="H30" s="7">
-        <f>SUM('Астрид'!H30,'Курортный'!H30,'Новое Колпино'!H30,'Таллинский парк'!H30)</f>
-        <v/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I30" s="7">
         <f>SUM('Астрид'!I30,'Курортный'!I30,'Новое Колпино'!I30,'Таллинский парк'!I30)</f>
@@ -2007,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM('Астрид'!B31,'Курортный'!B31,'Новое Колпино'!B31,'Таллинский парк'!B31)</f>
+        <f>SUM(C31,D31,E31,F31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2030,9 +2057,10 @@
         <f>SUM('Астрид'!G31,'Курортный'!G31,'Новое Колпино'!G31,'Таллинский парк'!G31)</f>
         <v/>
       </c>
-      <c r="H31" s="7">
-        <f>SUM('Астрид'!H31,'Курортный'!H31,'Новое Колпино'!H31,'Таллинский парк'!H31)</f>
-        <v/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" s="7">
         <f>SUM('Астрид'!I31,'Курортный'!I31,'Новое Колпино'!I31,'Таллинский парк'!I31)</f>
@@ -2057,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM('Астрид'!B32,'Курортный'!B32,'Новое Колпино'!B32,'Таллинский парк'!B32)</f>
+        <f>SUM(C32,D32,E32,F32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2080,9 +2108,10 @@
         <f>SUM('Астрид'!G32,'Курортный'!G32,'Новое Колпино'!G32,'Таллинский парк'!G32)</f>
         <v/>
       </c>
-      <c r="H32" s="7">
-        <f>SUM('Астрид'!H32,'Курортный'!H32,'Новое Колпино'!H32,'Таллинский парк'!H32)</f>
-        <v/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" s="7">
         <f>SUM('Астрид'!I32,'Курортный'!I32,'Новое Колпино'!I32,'Таллинский парк'!I32)</f>
@@ -2107,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM('Астрид'!B33,'Курортный'!B33,'Новое Колпино'!B33,'Таллинский парк'!B33)</f>
+        <f>SUM(C33,D33,E33,F33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2130,9 +2159,10 @@
         <f>SUM('Астрид'!G33,'Курортный'!G33,'Новое Колпино'!G33,'Таллинский парк'!G33)</f>
         <v/>
       </c>
-      <c r="H33" s="7">
-        <f>SUM('Астрид'!H33,'Курортный'!H33,'Новое Колпино'!H33,'Таллинский парк'!H33)</f>
-        <v/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I33" s="7">
         <f>SUM('Астрид'!I33,'Курортный'!I33,'Новое Колпино'!I33,'Таллинский парк'!I33)</f>
@@ -2180,9 +2210,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -2207,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM('Астрид'!B35,'Курортный'!B35,'Новое Колпино'!B35,'Таллинский парк'!B35)</f>
+        <f>SUM(C35,D35,E35,F35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2230,9 +2261,10 @@
         <f>SUM('Астрид'!G35,'Курортный'!G35,'Новое Колпино'!G35,'Таллинский парк'!G35)</f>
         <v/>
       </c>
-      <c r="H35" s="7">
-        <f>SUM('Астрид'!H35,'Курортный'!H35,'Новое Колпино'!H35,'Таллинский парк'!H35)</f>
-        <v/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" s="7">
         <f>SUM('Астрид'!I35,'Курортный'!I35,'Новое Колпино'!I35,'Таллинский парк'!I35)</f>
@@ -2257,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM('Астрид'!B36,'Курортный'!B36,'Новое Колпино'!B36,'Таллинский парк'!B36)</f>
+        <f>SUM(C36,D36,E36,F36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2280,9 +2312,10 @@
         <f>SUM('Астрид'!G36,'Курортный'!G36,'Новое Колпино'!G36,'Таллинский парк'!G36)</f>
         <v/>
       </c>
-      <c r="H36" s="7">
-        <f>SUM('Астрид'!H36,'Курортный'!H36,'Новое Колпино'!H36,'Таллинский парк'!H36)</f>
-        <v/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" s="7">
         <f>SUM('Астрид'!I36,'Курортный'!I36,'Новое Колпино'!I36,'Таллинский парк'!I36)</f>
@@ -2307,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM('Астрид'!B37,'Курортный'!B37,'Новое Колпино'!B37,'Таллинский парк'!B37)</f>
+        <f>SUM(C37,D37,E37,F37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2330,9 +2363,10 @@
         <f>SUM('Астрид'!G37,'Курортный'!G37,'Новое Колпино'!G37,'Таллинский парк'!G37)</f>
         <v/>
       </c>
-      <c r="H37" s="7">
-        <f>SUM('Астрид'!H37,'Курортный'!H37,'Новое Колпино'!H37,'Таллинский парк'!H37)</f>
-        <v/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" s="7">
         <f>SUM('Астрид'!I37,'Курортный'!I37,'Новое Колпино'!I37,'Таллинский парк'!I37)</f>
@@ -2357,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM('Астрид'!B38,'Курортный'!B38,'Новое Колпино'!B38,'Таллинский парк'!B38)</f>
+        <f>SUM(C38,D38,E38,F38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2380,9 +2414,10 @@
         <f>SUM('Астрид'!G38,'Курортный'!G38,'Новое Колпино'!G38,'Таллинский парк'!G38)</f>
         <v/>
       </c>
-      <c r="H38" s="7">
-        <f>SUM('Астрид'!H38,'Курортный'!H38,'Новое Колпино'!H38,'Таллинский парк'!H38)</f>
-        <v/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I38" s="7">
         <f>SUM('Астрид'!I38,'Курортный'!I38,'Новое Колпино'!I38,'Таллинский парк'!I38)</f>
@@ -2407,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM('Астрид'!B39,'Курортный'!B39,'Новое Колпино'!B39,'Таллинский парк'!B39)</f>
+        <f>SUM(C39,D39,E39,F39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2430,9 +2465,10 @@
         <f>SUM('Астрид'!G39,'Курортный'!G39,'Новое Колпино'!G39,'Таллинский парк'!G39)</f>
         <v/>
       </c>
-      <c r="H39" s="7">
-        <f>SUM('Астрид'!H39,'Курортный'!H39,'Новое Колпино'!H39,'Таллинский парк'!H39)</f>
-        <v/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I39" s="7">
         <f>SUM('Астрид'!I39,'Курортный'!I39,'Новое Колпино'!I39,'Таллинский парк'!I39)</f>
@@ -2457,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM('Астрид'!B40,'Курортный'!B40,'Новое Колпино'!B40,'Таллинский парк'!B40)</f>
+        <f>SUM(C40,D40,E40,F40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2480,9 +2516,10 @@
         <f>SUM('Астрид'!G40,'Курортный'!G40,'Новое Колпино'!G40,'Таллинский парк'!G40)</f>
         <v/>
       </c>
-      <c r="H40" s="7">
-        <f>SUM('Астрид'!H40,'Курортный'!H40,'Новое Колпино'!H40,'Таллинский парк'!H40)</f>
-        <v/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I40" s="7">
         <f>SUM('Астрид'!I40,'Курортный'!I40,'Новое Колпино'!I40,'Таллинский парк'!I40)</f>
@@ -2507,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM('Астрид'!B41,'Курортный'!B41,'Новое Колпино'!B41,'Таллинский парк'!B41)</f>
+        <f>SUM(C41,D41,E41,F41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2530,9 +2567,10 @@
         <f>SUM('Астрид'!G41,'Курортный'!G41,'Новое Колпино'!G41,'Таллинский парк'!G41)</f>
         <v/>
       </c>
-      <c r="H41" s="7">
-        <f>SUM('Астрид'!H41,'Курортный'!H41,'Новое Колпино'!H41,'Таллинский парк'!H41)</f>
-        <v/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" s="7">
         <f>SUM('Астрид'!I41,'Курортный'!I41,'Новое Колпино'!I41,'Таллинский парк'!I41)</f>
@@ -2557,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM('Астрид'!B42,'Курортный'!B42,'Новое Колпино'!B42,'Таллинский парк'!B42)</f>
+        <f>SUM(C42,D42,E42,F42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2580,9 +2618,10 @@
         <f>SUM('Астрид'!G42,'Курортный'!G42,'Новое Колпино'!G42,'Таллинский парк'!G42)</f>
         <v/>
       </c>
-      <c r="H42" s="7">
-        <f>SUM('Астрид'!H42,'Курортный'!H42,'Новое Колпино'!H42,'Таллинский парк'!H42)</f>
-        <v/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I42" s="7">
         <f>SUM('Астрид'!I42,'Курортный'!I42,'Новое Колпино'!I42,'Таллинский парк'!I42)</f>
@@ -2630,9 +2669,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -2680,9 +2720,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -2730,9 +2771,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -2757,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM('Астрид'!B46,'Курортный'!B46,'Новое Колпино'!B46,'Таллинский парк'!B46)</f>
+        <f>SUM(C46,D46,E46,F46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2780,9 +2822,10 @@
         <f>SUM('Астрид'!G46,'Курортный'!G46,'Новое Колпино'!G46,'Таллинский парк'!G46)</f>
         <v/>
       </c>
-      <c r="H46" s="7">
-        <f>SUM('Астрид'!H46,'Курортный'!H46,'Новое Колпино'!H46,'Таллинский парк'!H46)</f>
-        <v/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" s="7">
         <f>SUM('Астрид'!I46,'Курортный'!I46,'Новое Колпино'!I46,'Таллинский парк'!I46)</f>
@@ -2807,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM('Астрид'!B47,'Курортный'!B47,'Новое Колпино'!B47,'Таллинский парк'!B47)</f>
+        <f>SUM(C47,D47,E47,F47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2830,9 +2873,10 @@
         <f>SUM('Астрид'!G47,'Курортный'!G47,'Новое Колпино'!G47,'Таллинский парк'!G47)</f>
         <v/>
       </c>
-      <c r="H47" s="7">
-        <f>SUM('Астрид'!H47,'Курортный'!H47,'Новое Колпино'!H47,'Таллинский парк'!H47)</f>
-        <v/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I47" s="7">
         <f>SUM('Астрид'!I47,'Курортный'!I47,'Новое Колпино'!I47,'Таллинский парк'!I47)</f>
@@ -2880,9 +2924,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -2907,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM('Астрид'!B49,'Курортный'!B49,'Новое Колпино'!B49,'Таллинский парк'!B49)</f>
+        <f>SUM(C49,D49,E49,F49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -2930,9 +2975,10 @@
         <f>SUM('Астрид'!G49,'Курортный'!G49,'Новое Колпино'!G49,'Таллинский парк'!G49)</f>
         <v/>
       </c>
-      <c r="H49" s="7">
-        <f>SUM('Астрид'!H49,'Курортный'!H49,'Новое Колпино'!H49,'Таллинский парк'!H49)</f>
-        <v/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" s="7">
         <f>SUM('Астрид'!I49,'Курортный'!I49,'Новое Колпино'!I49,'Таллинский парк'!I49)</f>
@@ -2957,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM('Астрид'!B50,'Курортный'!B50,'Новое Колпино'!B50,'Таллинский парк'!B50)</f>
+        <f>SUM(C50,D50,E50,F50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -2980,9 +3026,10 @@
         <f>SUM('Астрид'!G50,'Курортный'!G50,'Новое Колпино'!G50,'Таллинский парк'!G50)</f>
         <v/>
       </c>
-      <c r="H50" s="7">
-        <f>SUM('Астрид'!H50,'Курортный'!H50,'Новое Колпино'!H50,'Таллинский парк'!H50)</f>
-        <v/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I50" s="7">
         <f>SUM('Астрид'!I50,'Курортный'!I50,'Новое Колпино'!I50,'Таллинский парк'!I50)</f>
@@ -3007,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM('Астрид'!B51,'Курортный'!B51,'Новое Колпино'!B51,'Таллинский парк'!B51)</f>
+        <f>SUM(C51,D51,E51,F51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3030,9 +3077,10 @@
         <f>SUM('Астрид'!G51,'Курортный'!G51,'Новое Колпино'!G51,'Таллинский парк'!G51)</f>
         <v/>
       </c>
-      <c r="H51" s="7">
-        <f>SUM('Астрид'!H51,'Курортный'!H51,'Новое Колпино'!H51,'Таллинский парк'!H51)</f>
-        <v/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I51" s="7">
         <f>SUM('Астрид'!I51,'Курортный'!I51,'Новое Колпино'!I51,'Таллинский парк'!I51)</f>
@@ -3080,9 +3128,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -3107,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM('Астрид'!B53,'Курортный'!B53,'Новое Колпино'!B53,'Таллинский парк'!B53)</f>
+        <f>SUM(C53,D53,E53,F53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3130,9 +3179,10 @@
         <f>SUM('Астрид'!G53,'Курортный'!G53,'Новое Колпино'!G53,'Таллинский парк'!G53)</f>
         <v/>
       </c>
-      <c r="H53" s="7">
-        <f>SUM('Астрид'!H53,'Курортный'!H53,'Новое Колпино'!H53,'Таллинский парк'!H53)</f>
-        <v/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I53" s="7">
         <f>SUM('Астрид'!I53,'Курортный'!I53,'Новое Колпино'!I53,'Таллинский парк'!I53)</f>
@@ -3157,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM('Астрид'!B54,'Курортный'!B54,'Новое Колпино'!B54,'Таллинский парк'!B54)</f>
+        <f>SUM(C54,D54,E54,F54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3180,9 +3230,10 @@
         <f>SUM('Астрид'!G54,'Курортный'!G54,'Новое Колпино'!G54,'Таллинский парк'!G54)</f>
         <v/>
       </c>
-      <c r="H54" s="7">
-        <f>SUM('Астрид'!H54,'Курортный'!H54,'Новое Колпино'!H54,'Таллинский парк'!H54)</f>
-        <v/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I54" s="7">
         <f>SUM('Астрид'!I54,'Курортный'!I54,'Новое Колпино'!I54,'Таллинский парк'!I54)</f>
@@ -3207,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM('Астрид'!B55,'Курортный'!B55,'Новое Колпино'!B55,'Таллинский парк'!B55)</f>
+        <f>SUM(C55,D55,E55,F55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3230,9 +3281,10 @@
         <f>SUM('Астрид'!G55,'Курортный'!G55,'Новое Колпино'!G55,'Таллинский парк'!G55)</f>
         <v/>
       </c>
-      <c r="H55" s="7">
-        <f>SUM('Астрид'!H55,'Курортный'!H55,'Новое Колпино'!H55,'Таллинский парк'!H55)</f>
-        <v/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I55" s="7">
         <f>SUM('Астрид'!I55,'Курортный'!I55,'Новое Колпино'!I55,'Таллинский парк'!I55)</f>
@@ -3257,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM('Астрид'!B56,'Курортный'!B56,'Новое Колпино'!B56,'Таллинский парк'!B56)</f>
+        <f>SUM(C56,D56,E56,F56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3280,9 +3332,10 @@
         <f>SUM('Астрид'!G56,'Курортный'!G56,'Новое Колпино'!G56,'Таллинский парк'!G56)</f>
         <v/>
       </c>
-      <c r="H56" s="7">
-        <f>SUM('Астрид'!H56,'Курортный'!H56,'Новое Колпино'!H56,'Таллинский парк'!H56)</f>
-        <v/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" s="7">
         <f>SUM('Астрид'!I56,'Курортный'!I56,'Новое Колпино'!I56,'Таллинский парк'!I56)</f>
@@ -3307,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM('Астрид'!B57,'Курортный'!B57,'Новое Колпино'!B57,'Таллинский парк'!B57)</f>
+        <f>SUM(C57,D57,E57,F57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3330,9 +3383,10 @@
         <f>SUM('Астрид'!G57,'Курортный'!G57,'Новое Колпино'!G57,'Таллинский парк'!G57)</f>
         <v/>
       </c>
-      <c r="H57" s="7">
-        <f>SUM('Астрид'!H57,'Курортный'!H57,'Новое Колпино'!H57,'Таллинский парк'!H57)</f>
-        <v/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" s="7">
         <f>SUM('Астрид'!I57,'Курортный'!I57,'Новое Колпино'!I57,'Таллинский парк'!I57)</f>
@@ -3357,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM('Астрид'!B58,'Курортный'!B58,'Новое Колпино'!B58,'Таллинский парк'!B58)</f>
+        <f>SUM(C58,D58,E58,F58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3380,9 +3434,10 @@
         <f>SUM('Астрид'!G58,'Курортный'!G58,'Новое Колпино'!G58,'Таллинский парк'!G58)</f>
         <v/>
       </c>
-      <c r="H58" s="7">
-        <f>SUM('Астрид'!H58,'Курортный'!H58,'Новое Колпино'!H58,'Таллинский парк'!H58)</f>
-        <v/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I58" s="7">
         <f>SUM('Астрид'!I58,'Курортный'!I58,'Новое Колпино'!I58,'Таллинский парк'!I58)</f>
@@ -3407,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM('Астрид'!B59,'Курортный'!B59,'Новое Колпино'!B59,'Таллинский парк'!B59)</f>
+        <f>SUM(C59,D59,E59,F59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3430,9 +3485,10 @@
         <f>SUM('Астрид'!G59,'Курортный'!G59,'Новое Колпино'!G59,'Таллинский парк'!G59)</f>
         <v/>
       </c>
-      <c r="H59" s="7">
-        <f>SUM('Астрид'!H59,'Курортный'!H59,'Новое Колпино'!H59,'Таллинский парк'!H59)</f>
-        <v/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" s="7">
         <f>SUM('Астрид'!I59,'Курортный'!I59,'Новое Колпино'!I59,'Таллинский парк'!I59)</f>
@@ -3480,9 +3536,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -3507,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM('Астрид'!B61,'Курортный'!B61,'Новое Колпино'!B61,'Таллинский парк'!B61)</f>
+        <f>SUM(C61,D61,E61,F61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3530,9 +3587,10 @@
         <f>SUM('Астрид'!G61,'Курортный'!G61,'Новое Колпино'!G61,'Таллинский парк'!G61)</f>
         <v/>
       </c>
-      <c r="H61" s="7">
-        <f>SUM('Астрид'!H61,'Курортный'!H61,'Новое Колпино'!H61,'Таллинский парк'!H61)</f>
-        <v/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I61" s="7">
         <f>SUM('Астрид'!I61,'Курортный'!I61,'Новое Колпино'!I61,'Таллинский парк'!I61)</f>
@@ -3557,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM('Астрид'!B62,'Курортный'!B62,'Новое Колпино'!B62,'Таллинский парк'!B62)</f>
+        <f>SUM(C62,D62,E62,F62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3580,9 +3638,10 @@
         <f>SUM('Астрид'!G62,'Курортный'!G62,'Новое Колпино'!G62,'Таллинский парк'!G62)</f>
         <v/>
       </c>
-      <c r="H62" s="7">
-        <f>SUM('Астрид'!H62,'Курортный'!H62,'Новое Колпино'!H62,'Таллинский парк'!H62)</f>
-        <v/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" s="7">
         <f>SUM('Астрид'!I62,'Курортный'!I62,'Новое Колпино'!I62,'Таллинский парк'!I62)</f>
@@ -3607,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM('Астрид'!B63,'Курортный'!B63,'Новое Колпино'!B63,'Таллинский парк'!B63)</f>
+        <f>SUM(C63,D63,E63,F63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3630,9 +3689,10 @@
         <f>SUM('Астрид'!G63,'Курортный'!G63,'Новое Колпино'!G63,'Таллинский парк'!G63)</f>
         <v/>
       </c>
-      <c r="H63" s="7">
-        <f>SUM('Астрид'!H63,'Курортный'!H63,'Новое Колпино'!H63,'Таллинский парк'!H63)</f>
-        <v/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I63" s="7">
         <f>SUM('Астрид'!I63,'Курортный'!I63,'Новое Колпино'!I63,'Таллинский парк'!I63)</f>
@@ -3657,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM('Астрид'!B64,'Курортный'!B64,'Новое Колпино'!B64,'Таллинский парк'!B64)</f>
+        <f>SUM(C64,D64,E64,F64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3680,9 +3740,10 @@
         <f>SUM('Астрид'!G64,'Курортный'!G64,'Новое Колпино'!G64,'Таллинский парк'!G64)</f>
         <v/>
       </c>
-      <c r="H64" s="7">
-        <f>SUM('Астрид'!H64,'Курортный'!H64,'Новое Колпино'!H64,'Таллинский парк'!H64)</f>
-        <v/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I64" s="7">
         <f>SUM('Астрид'!I64,'Курортный'!I64,'Новое Колпино'!I64,'Таллинский парк'!I64)</f>
@@ -3707,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM('Астрид'!B65,'Курортный'!B65,'Новое Колпино'!B65,'Таллинский парк'!B65)</f>
+        <f>SUM(C65,D65,E65,F65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3730,9 +3791,10 @@
         <f>SUM('Астрид'!G65,'Курортный'!G65,'Новое Колпино'!G65,'Таллинский парк'!G65)</f>
         <v/>
       </c>
-      <c r="H65" s="7">
-        <f>SUM('Астрид'!H65,'Курортный'!H65,'Новое Колпино'!H65,'Таллинский парк'!H65)</f>
-        <v/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I65" s="7">
         <f>SUM('Астрид'!I65,'Курортный'!I65,'Новое Колпино'!I65,'Таллинский парк'!I65)</f>
@@ -3757,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM('Астрид'!B66,'Курортный'!B66,'Новое Колпино'!B66,'Таллинский парк'!B66)</f>
+        <f>SUM(C66,D66,E66,F66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3780,9 +3842,10 @@
         <f>SUM('Астрид'!G66,'Курортный'!G66,'Новое Колпино'!G66,'Таллинский парк'!G66)</f>
         <v/>
       </c>
-      <c r="H66" s="7">
-        <f>SUM('Астрид'!H66,'Курортный'!H66,'Новое Колпино'!H66,'Таллинский парк'!H66)</f>
-        <v/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I66" s="7">
         <f>SUM('Астрид'!I66,'Курортный'!I66,'Новое Колпино'!I66,'Таллинский парк'!I66)</f>
@@ -3807,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM('Астрид'!B67,'Курортный'!B67,'Новое Колпино'!B67,'Таллинский парк'!B67)</f>
+        <f>SUM(C67,D67,E67,F67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3830,9 +3893,10 @@
         <f>SUM('Астрид'!G67,'Курортный'!G67,'Новое Колпино'!G67,'Таллинский парк'!G67)</f>
         <v/>
       </c>
-      <c r="H67" s="7">
-        <f>SUM('Астрид'!H67,'Курортный'!H67,'Новое Колпино'!H67,'Таллинский парк'!H67)</f>
-        <v/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I67" s="7">
         <f>SUM('Астрид'!I67,'Курортный'!I67,'Новое Колпино'!I67,'Таллинский парк'!I67)</f>
@@ -3857,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM('Астрид'!B68,'Курортный'!B68,'Новое Колпино'!B68,'Таллинский парк'!B68)</f>
+        <f>SUM(C68,D68,E68,F68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3880,9 +3944,10 @@
         <f>SUM('Астрид'!G68,'Курортный'!G68,'Новое Колпино'!G68,'Таллинский парк'!G68)</f>
         <v/>
       </c>
-      <c r="H68" s="7">
-        <f>SUM('Астрид'!H68,'Курортный'!H68,'Новое Колпино'!H68,'Таллинский парк'!H68)</f>
-        <v/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" s="7">
         <f>SUM('Астрид'!I68,'Курортный'!I68,'Новое Колпино'!I68,'Таллинский парк'!I68)</f>
@@ -3907,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM('Астрид'!B69,'Курортный'!B69,'Новое Колпино'!B69,'Таллинский парк'!B69)</f>
+        <f>SUM(C69,D69,E69,F69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -3930,9 +3995,10 @@
         <f>SUM('Астрид'!G69,'Курортный'!G69,'Новое Колпино'!G69,'Таллинский парк'!G69)</f>
         <v/>
       </c>
-      <c r="H69" s="7">
-        <f>SUM('Астрид'!H69,'Курортный'!H69,'Новое Колпино'!H69,'Таллинский парк'!H69)</f>
-        <v/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I69" s="7">
         <f>SUM('Астрид'!I69,'Курортный'!I69,'Новое Колпино'!I69,'Таллинский парк'!I69)</f>
@@ -3957,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM('Астрид'!B70,'Курортный'!B70,'Новое Колпино'!B70,'Таллинский парк'!B70)</f>
+        <f>SUM(C70,D70,E70,F70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -3980,9 +4046,10 @@
         <f>SUM('Астрид'!G70,'Курортный'!G70,'Новое Колпино'!G70,'Таллинский парк'!G70)</f>
         <v/>
       </c>
-      <c r="H70" s="7">
-        <f>SUM('Астрид'!H70,'Курортный'!H70,'Новое Колпино'!H70,'Таллинский парк'!H70)</f>
-        <v/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I70" s="7">
         <f>SUM('Астрид'!I70,'Курортный'!I70,'Новое Колпино'!I70,'Таллинский парк'!I70)</f>
@@ -4007,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM('Астрид'!B71,'Курортный'!B71,'Новое Колпино'!B71,'Таллинский парк'!B71)</f>
+        <f>SUM(C71,D71,E71,F71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4030,9 +4097,10 @@
         <f>SUM('Астрид'!G71,'Курортный'!G71,'Новое Колпино'!G71,'Таллинский парк'!G71)</f>
         <v/>
       </c>
-      <c r="H71" s="7">
-        <f>SUM('Астрид'!H71,'Курортный'!H71,'Новое Колпино'!H71,'Таллинский парк'!H71)</f>
-        <v/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I71" s="7">
         <f>SUM('Астрид'!I71,'Курортный'!I71,'Новое Колпино'!I71,'Таллинский парк'!I71)</f>
@@ -4057,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM('Астрид'!B72,'Курортный'!B72,'Новое Колпино'!B72,'Таллинский парк'!B72)</f>
+        <f>SUM(C72,D72,E72,F72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4080,9 +4148,10 @@
         <f>SUM('Астрид'!G72,'Курортный'!G72,'Новое Колпино'!G72,'Таллинский парк'!G72)</f>
         <v/>
       </c>
-      <c r="H72" s="7">
-        <f>SUM('Астрид'!H72,'Курортный'!H72,'Новое Колпино'!H72,'Таллинский парк'!H72)</f>
-        <v/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I72" s="7">
         <f>SUM('Астрид'!I72,'Курортный'!I72,'Новое Колпино'!I72,'Таллинский парк'!I72)</f>
@@ -4107,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM('Астрид'!B73,'Курортный'!B73,'Новое Колпино'!B73,'Таллинский парк'!B73)</f>
+        <f>SUM(C73,D73,E73,F73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4130,9 +4199,10 @@
         <f>SUM('Астрид'!G73,'Курортный'!G73,'Новое Колпино'!G73,'Таллинский парк'!G73)</f>
         <v/>
       </c>
-      <c r="H73" s="7">
-        <f>SUM('Астрид'!H73,'Курортный'!H73,'Новое Колпино'!H73,'Таллинский парк'!H73)</f>
-        <v/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" s="7">
         <f>SUM('Астрид'!I73,'Курортный'!I73,'Новое Колпино'!I73,'Таллинский парк'!I73)</f>
@@ -4157,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM('Астрид'!B74,'Курортный'!B74,'Новое Колпино'!B74,'Таллинский парк'!B74)</f>
+        <f>SUM(C74,D74,E74,F74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4180,9 +4250,10 @@
         <f>SUM('Астрид'!G74,'Курортный'!G74,'Новое Колпино'!G74,'Таллинский парк'!G74)</f>
         <v/>
       </c>
-      <c r="H74" s="7">
-        <f>SUM('Астрид'!H74,'Курортный'!H74,'Новое Колпино'!H74,'Таллинский парк'!H74)</f>
-        <v/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I74" s="7">
         <f>SUM('Астрид'!I74,'Курортный'!I74,'Новое Колпино'!I74,'Таллинский парк'!I74)</f>
@@ -4207,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM('Астрид'!B75,'Курортный'!B75,'Новое Колпино'!B75,'Таллинский парк'!B75)</f>
+        <f>SUM(C75,D75,E75,F75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4230,9 +4301,10 @@
         <f>SUM('Астрид'!G75,'Курортный'!G75,'Новое Колпино'!G75,'Таллинский парк'!G75)</f>
         <v/>
       </c>
-      <c r="H75" s="7">
-        <f>SUM('Астрид'!H75,'Курортный'!H75,'Новое Колпино'!H75,'Таллинский парк'!H75)</f>
-        <v/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I75" s="7">
         <f>SUM('Астрид'!I75,'Курортный'!I75,'Новое Колпино'!I75,'Таллинский парк'!I75)</f>
@@ -4257,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM('Астрид'!B76,'Курортный'!B76,'Новое Колпино'!B76,'Таллинский парк'!B76)</f>
+        <f>SUM(C76,D76,E76,F76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4280,9 +4352,10 @@
         <f>SUM('Астрид'!G76,'Курортный'!G76,'Новое Колпино'!G76,'Таллинский парк'!G76)</f>
         <v/>
       </c>
-      <c r="H76" s="7">
-        <f>SUM('Астрид'!H76,'Курортный'!H76,'Новое Колпино'!H76,'Таллинский парк'!H76)</f>
-        <v/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" s="7">
         <f>SUM('Астрид'!I76,'Курортный'!I76,'Новое Колпино'!I76,'Таллинский парк'!I76)</f>
@@ -4307,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM('Астрид'!B77,'Курортный'!B77,'Новое Колпино'!B77,'Таллинский парк'!B77)</f>
+        <f>SUM(C77,D77,E77,F77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4330,9 +4403,10 @@
         <f>SUM('Астрид'!G77,'Курортный'!G77,'Новое Колпино'!G77,'Таллинский парк'!G77)</f>
         <v/>
       </c>
-      <c r="H77" s="7">
-        <f>SUM('Астрид'!H77,'Курортный'!H77,'Новое Колпино'!H77,'Таллинский парк'!H77)</f>
-        <v/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" s="7">
         <f>SUM('Астрид'!I77,'Курортный'!I77,'Новое Колпино'!I77,'Таллинский парк'!I77)</f>
@@ -4357,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM('Астрид'!B78,'Курортный'!B78,'Новое Колпино'!B78,'Таллинский парк'!B78)</f>
+        <f>SUM(C78,D78,E78,F78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4380,9 +4454,10 @@
         <f>SUM('Астрид'!G78,'Курортный'!G78,'Новое Колпино'!G78,'Таллинский парк'!G78)</f>
         <v/>
       </c>
-      <c r="H78" s="7">
-        <f>SUM('Астрид'!H78,'Курортный'!H78,'Новое Колпино'!H78,'Таллинский парк'!H78)</f>
-        <v/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" s="7">
         <f>SUM('Астрид'!I78,'Курортный'!I78,'Новое Колпино'!I78,'Таллинский парк'!I78)</f>
@@ -4407,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM('Астрид'!B79,'Курортный'!B79,'Новое Колпино'!B79,'Таллинский парк'!B79)</f>
+        <f>SUM(C79,D79,E79,F79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4430,9 +4505,10 @@
         <f>SUM('Астрид'!G79,'Курортный'!G79,'Новое Колпино'!G79,'Таллинский парк'!G79)</f>
         <v/>
       </c>
-      <c r="H79" s="7">
-        <f>SUM('Астрид'!H79,'Курортный'!H79,'Новое Колпино'!H79,'Таллинский парк'!H79)</f>
-        <v/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I79" s="7">
         <f>SUM('Астрид'!I79,'Курортный'!I79,'Новое Колпино'!I79,'Таллинский парк'!I79)</f>
@@ -4480,9 +4556,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -4530,9 +4607,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -4580,9 +4658,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -4607,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM('Астрид'!B83,'Курортный'!B83,'Новое Колпино'!B83,'Таллинский парк'!B83)</f>
+        <f>SUM(C83,D83,E83,F83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4630,9 +4709,10 @@
         <f>SUM('Астрид'!G83,'Курортный'!G83,'Новое Колпино'!G83,'Таллинский парк'!G83)</f>
         <v/>
       </c>
-      <c r="H83" s="7">
-        <f>SUM('Астрид'!H83,'Курортный'!H83,'Новое Колпино'!H83,'Таллинский парк'!H83)</f>
-        <v/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I83" s="7">
         <f>SUM('Астрид'!I83,'Курортный'!I83,'Новое Колпино'!I83,'Таллинский парк'!I83)</f>
@@ -4657,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM('Астрид'!B84,'Курортный'!B84,'Новое Колпино'!B84,'Таллинский парк'!B84)</f>
+        <f>SUM(C84,D84,E84,F84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4680,9 +4760,10 @@
         <f>SUM('Астрид'!G84,'Курортный'!G84,'Новое Колпино'!G84,'Таллинский парк'!G84)</f>
         <v/>
       </c>
-      <c r="H84" s="7">
-        <f>SUM('Астрид'!H84,'Курортный'!H84,'Новое Колпино'!H84,'Таллинский парк'!H84)</f>
-        <v/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I84" s="7">
         <f>SUM('Астрид'!I84,'Курортный'!I84,'Новое Колпино'!I84,'Таллинский парк'!I84)</f>
@@ -4707,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM('Астрид'!B85,'Курортный'!B85,'Новое Колпино'!B85,'Таллинский парк'!B85)</f>
+        <f>SUM(C85,D85,E85,F85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4730,9 +4811,10 @@
         <f>SUM('Астрид'!G85,'Курортный'!G85,'Новое Колпино'!G85,'Таллинский парк'!G85)</f>
         <v/>
       </c>
-      <c r="H85" s="7">
-        <f>SUM('Астрид'!H85,'Курортный'!H85,'Новое Колпино'!H85,'Таллинский парк'!H85)</f>
-        <v/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I85" s="7">
         <f>SUM('Астрид'!I85,'Курортный'!I85,'Новое Колпино'!I85,'Таллинский парк'!I85)</f>
@@ -4757,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM('Астрид'!B86,'Курортный'!B86,'Новое Колпино'!B86,'Таллинский парк'!B86)</f>
+        <f>SUM(C86,D86,E86,F86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4780,9 +4862,10 @@
         <f>SUM('Астрид'!G86,'Курортный'!G86,'Новое Колпино'!G86,'Таллинский парк'!G86)</f>
         <v/>
       </c>
-      <c r="H86" s="7">
-        <f>SUM('Астрид'!H86,'Курортный'!H86,'Новое Колпино'!H86,'Таллинский парк'!H86)</f>
-        <v/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I86" s="7">
         <f>SUM('Астрид'!I86,'Курортный'!I86,'Новое Колпино'!I86,'Таллинский парк'!I86)</f>
@@ -4830,9 +4913,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -4857,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM('Астрид'!B88,'Курортный'!B88,'Новое Колпино'!B88,'Таллинский парк'!B88)</f>
+        <f>SUM(C88,D88,E88,F88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -4880,9 +4964,10 @@
         <f>SUM('Астрид'!G88,'Курортный'!G88,'Новое Колпино'!G88,'Таллинский парк'!G88)</f>
         <v/>
       </c>
-      <c r="H88" s="7">
-        <f>SUM('Астрид'!H88,'Курортный'!H88,'Новое Колпино'!H88,'Таллинский парк'!H88)</f>
-        <v/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I88" s="7">
         <f>SUM('Астрид'!I88,'Курортный'!I88,'Новое Колпино'!I88,'Таллинский парк'!I88)</f>
@@ -4930,9 +5015,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -4980,9 +5066,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -5030,9 +5117,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -5057,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM('Астрид'!B92,'Курортный'!B92,'Новое Колпино'!B92,'Таллинский парк'!B92)</f>
+        <f>SUM(C92,D92,E92,F92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5080,9 +5168,10 @@
         <f>SUM('Астрид'!G92,'Курортный'!G92,'Новое Колпино'!G92,'Таллинский парк'!G92)</f>
         <v/>
       </c>
-      <c r="H92" s="7">
-        <f>SUM('Астрид'!H92,'Курортный'!H92,'Новое Колпино'!H92,'Таллинский парк'!H92)</f>
-        <v/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" s="7">
         <f>SUM('Астрид'!I92,'Курортный'!I92,'Новое Колпино'!I92,'Таллинский парк'!I92)</f>
@@ -5107,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM('Астрид'!B93,'Курортный'!B93,'Новое Колпино'!B93,'Таллинский парк'!B93)</f>
+        <f>SUM(C93,D93,E93,F93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5130,9 +5219,10 @@
         <f>SUM('Астрид'!G93,'Курортный'!G93,'Новое Колпино'!G93,'Таллинский парк'!G93)</f>
         <v/>
       </c>
-      <c r="H93" s="7">
-        <f>SUM('Астрид'!H93,'Курортный'!H93,'Новое Колпино'!H93,'Таллинский парк'!H93)</f>
-        <v/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I93" s="7">
         <f>SUM('Астрид'!I93,'Курортный'!I93,'Новое Колпино'!I93,'Таллинский парк'!I93)</f>
@@ -5157,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM('Астрид'!B94,'Курортный'!B94,'Новое Колпино'!B94,'Таллинский парк'!B94)</f>
+        <f>SUM(C94,D94,E94,F94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5180,9 +5270,10 @@
         <f>SUM('Астрид'!G94,'Курортный'!G94,'Новое Колпино'!G94,'Таллинский парк'!G94)</f>
         <v/>
       </c>
-      <c r="H94" s="7">
-        <f>SUM('Астрид'!H94,'Курортный'!H94,'Новое Колпино'!H94,'Таллинский парк'!H94)</f>
-        <v/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I94" s="7">
         <f>SUM('Астрид'!I94,'Курортный'!I94,'Новое Колпино'!I94,'Таллинский парк'!I94)</f>
@@ -5230,9 +5321,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -5257,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM('Астрид'!B96,'Курортный'!B96,'Новое Колпино'!B96,'Таллинский парк'!B96)</f>
+        <f>SUM(C96,D96,E96,F96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5280,9 +5372,10 @@
         <f>SUM('Астрид'!G96,'Курортный'!G96,'Новое Колпино'!G96,'Таллинский парк'!G96)</f>
         <v/>
       </c>
-      <c r="H96" s="7">
-        <f>SUM('Астрид'!H96,'Курортный'!H96,'Новое Колпино'!H96,'Таллинский парк'!H96)</f>
-        <v/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="7">
         <f>SUM('Астрид'!I96,'Курортный'!I96,'Новое Колпино'!I96,'Таллинский парк'!I96)</f>
@@ -5307,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM('Астрид'!B97,'Курортный'!B97,'Новое Колпино'!B97,'Таллинский парк'!B97)</f>
+        <f>SUM(C97,D97,E97,F97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5330,9 +5423,10 @@
         <f>SUM('Астрид'!G97,'Курортный'!G97,'Новое Колпино'!G97,'Таллинский парк'!G97)</f>
         <v/>
       </c>
-      <c r="H97" s="7">
-        <f>SUM('Астрид'!H97,'Курортный'!H97,'Новое Колпино'!H97,'Таллинский парк'!H97)</f>
-        <v/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" s="7">
         <f>SUM('Астрид'!I97,'Курортный'!I97,'Новое Колпино'!I97,'Таллинский парк'!I97)</f>
@@ -5380,9 +5474,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -5430,9 +5525,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -5639,9 +5735,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -5665,10 +5762,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5747,9 +5843,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -5773,8 +5870,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2615842.28</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>228370.58</v>
@@ -5793,8 +5891,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n">
-        <v>653960.5699999999</v>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -5819,8 +5919,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>470000</v>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5873,10 +5974,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -5955,9 +6055,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -5981,10 +6082,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6039,10 +6139,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -6121,9 +6220,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -6147,10 +6247,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6205,10 +6304,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -6263,10 +6361,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -6321,8 +6418,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>51587.92</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>10587.92</v>
@@ -6341,8 +6439,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H17" s="7" t="n">
-        <v>10000</v>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -6367,8 +6467,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>20000</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -6391,8 +6492,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n">
-        <v>5000</v>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -6417,10 +6520,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6475,10 +6577,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6533,8 +6634,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>840120</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>209688.53</v>
@@ -6553,8 +6655,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n">
-        <v>210030</v>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -6579,8 +6683,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>1032000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>294494.09</v>
@@ -6599,8 +6704,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="7" t="n">
-        <v>258000</v>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -6625,8 +6732,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>190800</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>19188.5</v>
@@ -6645,8 +6753,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n">
-        <v>42000</v>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -6671,8 +6781,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>5012.59</v>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="n">
         <v>13380.59</v>
@@ -6721,10 +6832,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -6779,10 +6889,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6837,10 +6946,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -6895,10 +7003,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -6953,10 +7060,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7011,10 +7117,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>1019</v>
@@ -7065,10 +7170,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7123,10 +7227,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7181,10 +7284,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7263,9 +7365,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -7289,8 +7392,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>15000</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>10000</v>
@@ -7309,8 +7413,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="7" t="n">
-        <v>2500</v>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -7335,8 +7441,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>240000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>60000</v>
@@ -7355,8 +7462,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="7" t="n">
-        <v>60000</v>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
@@ -7381,8 +7490,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>4000</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -7401,8 +7511,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="7" t="n">
-        <v>1000</v>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -7427,10 +7539,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7485,8 +7596,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>147840</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>26500</v>
@@ -7505,8 +7617,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="7" t="n">
-        <v>36960</v>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -7531,10 +7645,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7589,10 +7702,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -7643,10 +7755,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7725,9 +7836,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -7775,9 +7887,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -7825,9 +7938,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -7851,8 +7965,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>339676.8</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>55821.21</v>
@@ -7871,8 +7986,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="7" t="n">
-        <v>84919.2</v>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
@@ -7897,10 +8014,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -7979,9 +8095,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -8005,10 +8122,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8063,10 +8179,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8121,10 +8236,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8203,9 +8317,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -8229,10 +8344,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8287,10 +8401,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8345,10 +8458,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8403,10 +8515,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8461,10 +8572,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8519,10 +8629,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8577,10 +8686,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8659,9 +8767,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -8685,10 +8794,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8743,10 +8851,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8801,10 +8908,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -8859,10 +8965,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -8917,10 +9022,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -8975,10 +9079,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9033,10 +9136,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9091,10 +9193,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9149,10 +9250,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9207,10 +9307,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9265,10 +9364,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9323,10 +9421,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9381,10 +9478,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9439,10 +9535,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9497,10 +9592,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9555,10 +9649,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9613,10 +9706,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9671,10 +9763,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9729,10 +9820,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9811,9 +9901,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -9861,9 +9952,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -9911,9 +10003,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -9937,10 +10030,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -9995,10 +10087,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10053,10 +10144,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10111,10 +10201,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10193,9 +10282,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -10219,10 +10309,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10301,9 +10390,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -10351,9 +10441,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -10401,9 +10492,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -10427,10 +10519,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10485,10 +10576,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10543,10 +10633,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10625,9 +10714,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -10651,8 +10741,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>40000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
@@ -10675,8 +10766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" s="7" t="n">
-        <v>10000</v>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
@@ -10701,8 +10794,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>124563.96</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>38678.65</v>
@@ -10721,8 +10815,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="7" t="n">
-        <v>31140.99</v>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
@@ -10771,9 +10867,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -10821,9 +10918,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -11030,9 +11128,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -11056,10 +11155,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11138,9 +11236,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -11164,8 +11263,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>5197391.32</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>1299347.83</v>
@@ -11212,8 +11312,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>2756163.38</v>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="n">
         <v>772382</v>
@@ -11260,10 +11361,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11342,9 +11442,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -11368,10 +11469,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11426,10 +11526,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11508,9 +11607,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -11534,10 +11634,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11592,10 +11691,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11650,10 +11748,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11708,8 +11805,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>40000</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>10000</v>
@@ -11756,8 +11854,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>22999</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>7999</v>
@@ -11804,10 +11903,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -11862,10 +11960,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -11920,8 +12017,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>2690034.97</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>695034.97</v>
@@ -11968,8 +12066,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>2400000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>600000</v>
@@ -12016,8 +12115,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>299800</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>60061</v>
@@ -12064,8 +12164,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>112000</v>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="n">
         <v>28000</v>
@@ -12112,10 +12213,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12170,10 +12270,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12228,10 +12327,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -12286,8 +12384,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>7069</v>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="n">
         <v>7069</v>
@@ -12340,10 +12439,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12398,8 +12496,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>12000</v>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -12446,10 +12545,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12504,10 +12602,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12562,10 +12659,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12644,9 +12740,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -12670,8 +12767,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>10000</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>2500</v>
@@ -12718,8 +12816,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>440000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>110000</v>
@@ -12766,8 +12865,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>14004.04</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>3504.04</v>
@@ -12814,10 +12914,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -12872,8 +12971,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>382200</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>95550</v>
@@ -12920,10 +13020,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -12978,8 +13077,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>16000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>4000</v>
@@ -13026,8 +13126,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
-        <v>179440.43</v>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="n">
         <v>44440.43</v>
@@ -13098,9 +13199,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -13148,9 +13250,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -13198,9 +13301,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -13224,8 +13328,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>556192.48</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>139048.12</v>
@@ -13272,10 +13377,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13354,9 +13458,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -13380,10 +13485,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13438,10 +13542,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13496,10 +13599,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13578,9 +13680,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -13604,10 +13707,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13662,10 +13764,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13720,10 +13821,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -13778,10 +13878,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -13836,10 +13935,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -13894,10 +13992,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -13952,10 +14049,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14034,9 +14130,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -14060,10 +14157,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14118,10 +14214,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14176,10 +14271,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14234,10 +14328,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14292,10 +14385,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14350,10 +14442,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14408,10 +14499,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14466,10 +14556,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14524,10 +14613,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14582,10 +14670,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14640,10 +14727,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14698,10 +14784,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14756,10 +14841,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -14814,10 +14898,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -14872,10 +14955,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -14930,10 +15012,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -14988,10 +15069,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15046,10 +15126,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15104,10 +15183,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15186,9 +15264,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -15236,9 +15315,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -15286,9 +15366,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -15312,10 +15393,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15370,10 +15450,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15428,10 +15507,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15486,10 +15564,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15568,9 +15645,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -15594,10 +15672,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15676,9 +15753,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -15726,9 +15804,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -15776,9 +15855,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -15802,10 +15882,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -15860,10 +15939,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -15918,10 +15996,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16000,9 +16077,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -16026,8 +16104,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>112000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>28000</v>
@@ -16074,8 +16153,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>378361.28</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>94590.32000000001</v>
@@ -16146,9 +16226,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -16196,9 +16277,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -16405,9 +16487,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -16431,10 +16514,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16513,9 +16595,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -16539,8 +16622,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>10175223.66</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>2759091.96</v>
@@ -16587,10 +16671,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16645,10 +16728,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16727,9 +16809,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -16753,10 +16836,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -16811,10 +16893,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -16893,9 +16974,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -16919,10 +17001,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -16977,8 +17058,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>352000</v>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="n">
         <v>88000</v>
@@ -17025,10 +17107,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17083,8 +17164,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>133810.13</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>43810.13</v>
@@ -17131,8 +17213,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>85901.39999999999</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>5901.4</v>
@@ -17179,10 +17262,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17237,8 +17319,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>30000</v>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -17291,8 +17374,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>2740000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>685000</v>
@@ -17339,8 +17423,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>3718084.67</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>958084.67</v>
@@ -17387,8 +17472,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>112000</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>28000</v>
@@ -17435,8 +17521,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>574820</v>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="n">
         <v>143705</v>
@@ -17483,10 +17570,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -17541,10 +17627,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17599,10 +17684,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17657,10 +17741,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17715,10 +17798,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -17773,8 +17855,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>12000</v>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -17821,10 +17904,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -17879,10 +17961,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -17937,10 +18018,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18019,9 +18099,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -18045,8 +18126,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>20000</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>5000</v>
@@ -18093,8 +18175,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>400000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>100000</v>
@@ -18141,8 +18224,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>20000</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>5000</v>
@@ -18189,10 +18273,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18247,8 +18330,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>477400</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>119350</v>
@@ -18295,10 +18379,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18353,8 +18436,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>8000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -18401,10 +18485,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18483,9 +18566,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -18533,9 +18617,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -18583,9 +18668,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -18609,8 +18695,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>1182777.16</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>295694.29</v>
@@ -18657,10 +18744,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18739,9 +18825,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -18765,10 +18852,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -18823,10 +18909,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -18881,10 +18966,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -18963,9 +19047,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -18989,10 +19074,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -19047,10 +19131,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19105,8 +19188,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
-        <v>12000</v>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="n">
         <v>3000</v>
@@ -19153,10 +19237,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -19211,10 +19294,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19269,10 +19351,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19327,10 +19408,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19409,9 +19489,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -19435,10 +19516,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19493,10 +19573,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19551,10 +19630,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19609,10 +19687,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19667,10 +19744,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19725,10 +19801,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -19783,10 +19858,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -19841,10 +19915,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -19899,10 +19972,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -19957,10 +20029,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20015,10 +20086,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20073,10 +20143,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20131,10 +20200,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20189,10 +20257,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20247,10 +20314,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20305,10 +20371,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20363,10 +20428,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20421,10 +20485,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20479,10 +20542,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20561,9 +20623,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -20611,9 +20674,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -20661,9 +20725,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -20687,10 +20752,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -20745,10 +20809,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -20803,10 +20866,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -20861,10 +20923,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -20943,9 +21004,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -20969,10 +21031,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21051,9 +21112,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -21101,9 +21163,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -21151,9 +21214,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -21177,10 +21241,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21235,10 +21298,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21293,10 +21355,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21375,9 +21436,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -21401,8 +21463,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>168000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>42000</v>
@@ -21449,8 +21512,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>470865.48</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>117716.37</v>
@@ -21521,9 +21585,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -21571,9 +21636,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -21780,9 +21846,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -21806,10 +21873,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -21888,9 +21954,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -21914,8 +21981,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>6397856.92</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>1599464.23</v>
@@ -21962,10 +22030,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22020,10 +22087,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22102,9 +22168,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -22128,10 +22195,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22186,8 +22252,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>15000</v>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="n">
         <v>15000</v>
@@ -22264,9 +22331,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -22290,10 +22358,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22348,10 +22415,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22406,10 +22472,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22464,8 +22529,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>9525</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>525</v>
@@ -22512,8 +22578,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>48381</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>33381</v>
@@ -22560,8 +22627,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>18000</v>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="n">
         <v>18000</v>
@@ -22614,10 +22682,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22672,8 +22739,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>1056000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>264000</v>
@@ -22720,8 +22788,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>1582778</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>532778</v>
@@ -22768,8 +22837,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>53052.57</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>11052.57</v>
@@ -22816,10 +22886,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -22874,10 +22943,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -22932,10 +23000,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -22990,10 +23057,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23048,10 +23114,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23106,10 +23171,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23164,10 +23228,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -23222,10 +23285,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -23280,10 +23342,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23338,10 +23399,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23420,9 +23480,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -23446,8 +23507,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>32500</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>12500</v>
@@ -23494,8 +23556,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>480000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>120000</v>
@@ -23542,8 +23605,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>8000</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -23590,10 +23654,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23648,8 +23711,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>205800</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>51450</v>
@@ -23696,10 +23760,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -23754,8 +23817,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>8000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -23802,10 +23866,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -23884,9 +23947,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -23934,9 +23998,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -23984,9 +24049,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -24010,8 +24076,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>394222.48</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>98555.62</v>
@@ -24058,10 +24125,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24140,9 +24206,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -24166,10 +24233,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24224,10 +24290,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24282,10 +24347,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24364,9 +24428,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -24390,10 +24455,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24448,10 +24512,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24506,10 +24569,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24564,10 +24626,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24622,10 +24683,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24680,10 +24740,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -24738,10 +24797,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -24820,9 +24878,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -24846,10 +24905,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -24904,10 +24962,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -24962,10 +25019,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25020,10 +25076,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25078,10 +25133,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25136,10 +25190,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25194,10 +25247,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25252,10 +25304,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25310,10 +25361,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25368,10 +25418,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25426,10 +25475,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25484,10 +25532,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25542,10 +25589,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25600,10 +25646,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25658,10 +25703,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -25716,10 +25760,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -25774,10 +25817,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -25832,10 +25874,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -25890,10 +25931,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -25972,9 +26012,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -26022,9 +26063,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -26072,9 +26114,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -26098,10 +26141,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26156,10 +26198,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26214,10 +26255,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26272,10 +26312,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26354,9 +26393,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -26380,10 +26420,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26462,9 +26501,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -26512,9 +26552,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -26562,9 +26603,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -26588,10 +26630,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26646,10 +26687,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -26704,10 +26744,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -26786,9 +26825,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -26812,8 +26852,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>96000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>24000</v>
@@ -26860,8 +26901,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>304659.92</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>76164.98</v>
@@ -26932,9 +26974,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -26982,9 +27025,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>

--- a/budget/output/Сводный бюджет СПб2.xlsx
+++ b/budget/output/Сводный бюджет СПб2.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
+        <f>SUM('Астрид'!B5,'Курортный'!B5,'Новое Колпино'!B5,'Таллинский парк'!B5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
+        <f>SUM('Астрид'!B7,'Курортный'!B7,'Новое Колпино'!B7,'Таллинский парк'!B7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
+        <f>SUM('Астрид'!B8,'Курортный'!B8,'Новое Колпино'!B8,'Таллинский парк'!B8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
+        <f>SUM('Астрид'!B9,'Курортный'!B9,'Новое Колпино'!B9,'Таллинский парк'!B9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
+        <f>SUM('Астрид'!B11,'Курортный'!B11,'Новое Колпино'!B11,'Таллинский парк'!B11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
+        <f>SUM('Астрид'!B12,'Курортный'!B12,'Новое Колпино'!B12,'Таллинский парк'!B12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
+        <f>SUM('Астрид'!B14,'Курортный'!B14,'Новое Колпино'!B14,'Таллинский парк'!B14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
+        <f>SUM('Астрид'!B15,'Курортный'!B15,'Новое Колпино'!B15,'Таллинский парк'!B15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
+        <f>SUM('Астрид'!B16,'Курортный'!B16,'Новое Колпино'!B16,'Таллинский парк'!B16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
+        <f>SUM('Астрид'!B17,'Курортный'!B17,'Новое Колпино'!B17,'Таллинский парк'!B17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
+        <f>SUM('Астрид'!B18,'Курортный'!B18,'Новое Колпино'!B18,'Таллинский парк'!B18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
+        <f>SUM('Астрид'!B19,'Курортный'!B19,'Новое Колпино'!B19,'Таллинский парк'!B19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
+        <f>SUM('Астрид'!B20,'Курортный'!B20,'Новое Колпино'!B20,'Таллинский парк'!B20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
+        <f>SUM('Астрид'!B21,'Курортный'!B21,'Новое Колпино'!B21,'Таллинский парк'!B21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
+        <f>SUM('Астрид'!B22,'Курортный'!B22,'Новое Колпино'!B22,'Таллинский парк'!B22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
+        <f>SUM('Астрид'!B23,'Курортный'!B23,'Новое Колпино'!B23,'Таллинский парк'!B23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
+        <f>SUM('Астрид'!B24,'Курортный'!B24,'Новое Колпино'!B24,'Таллинский парк'!B24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
+        <f>SUM('Астрид'!B25,'Курортный'!B25,'Новое Колпино'!B25,'Таллинский парк'!B25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
+        <f>SUM('Астрид'!B26,'Курортный'!B26,'Новое Колпино'!B26,'Таллинский парк'!B26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
+        <f>SUM('Астрид'!B27,'Курортный'!B27,'Новое Колпино'!B27,'Таллинский парк'!B27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
+        <f>SUM('Астрид'!B28,'Курортный'!B28,'Новое Колпино'!B28,'Таллинский парк'!B28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
+        <f>SUM('Астрид'!B29,'Курортный'!B29,'Новое Колпино'!B29,'Таллинский парк'!B29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
+        <f>SUM('Астрид'!B30,'Курортный'!B30,'Новое Колпино'!B30,'Таллинский парк'!B30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
+        <f>SUM('Астрид'!B31,'Курортный'!B31,'Новое Колпино'!B31,'Таллинский парк'!B31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
+        <f>SUM('Астрид'!B32,'Курортный'!B32,'Новое Колпино'!B32,'Таллинский парк'!B32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
+        <f>SUM('Астрид'!B33,'Курортный'!B33,'Новое Колпино'!B33,'Таллинский парк'!B33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
+        <f>SUM('Астрид'!B35,'Курортный'!B35,'Новое Колпино'!B35,'Таллинский парк'!B35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
+        <f>SUM('Астрид'!B36,'Курортный'!B36,'Новое Колпино'!B36,'Таллинский парк'!B36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
+        <f>SUM('Астрид'!B37,'Курортный'!B37,'Новое Колпино'!B37,'Таллинский парк'!B37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
+        <f>SUM('Астрид'!B38,'Курортный'!B38,'Новое Колпино'!B38,'Таллинский парк'!B38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
+        <f>SUM('Астрид'!B39,'Курортный'!B39,'Новое Колпино'!B39,'Таллинский парк'!B39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
+        <f>SUM('Астрид'!B40,'Курортный'!B40,'Новое Колпино'!B40,'Таллинский парк'!B40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
+        <f>SUM('Астрид'!B41,'Курортный'!B41,'Новое Колпино'!B41,'Таллинский парк'!B41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
+        <f>SUM('Астрид'!B42,'Курортный'!B42,'Новое Колпино'!B42,'Таллинский парк'!B42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
+        <f>SUM('Астрид'!B46,'Курортный'!B46,'Новое Колпино'!B46,'Таллинский парк'!B46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
+        <f>SUM('Астрид'!B47,'Курортный'!B47,'Новое Колпино'!B47,'Таллинский парк'!B47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
+        <f>SUM('Астрид'!B49,'Курортный'!B49,'Новое Колпино'!B49,'Таллинский парк'!B49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
+        <f>SUM('Астрид'!B50,'Курортный'!B50,'Новое Колпино'!B50,'Таллинский парк'!B50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
+        <f>SUM('Астрид'!B51,'Курортный'!B51,'Новое Колпино'!B51,'Таллинский парк'!B51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
+        <f>SUM('Астрид'!B53,'Курортный'!B53,'Новое Колпино'!B53,'Таллинский парк'!B53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
+        <f>SUM('Астрид'!B54,'Курортный'!B54,'Новое Колпино'!B54,'Таллинский парк'!B54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
+        <f>SUM('Астрид'!B55,'Курортный'!B55,'Новое Колпино'!B55,'Таллинский парк'!B55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
+        <f>SUM('Астрид'!B56,'Курортный'!B56,'Новое Колпино'!B56,'Таллинский парк'!B56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
+        <f>SUM('Астрид'!B57,'Курортный'!B57,'Новое Колпино'!B57,'Таллинский парк'!B57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
+        <f>SUM('Астрид'!B58,'Курортный'!B58,'Новое Колпино'!B58,'Таллинский парк'!B58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
+        <f>SUM('Астрид'!B59,'Курортный'!B59,'Новое Колпино'!B59,'Таллинский парк'!B59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
+        <f>SUM('Астрид'!B61,'Курортный'!B61,'Новое Колпино'!B61,'Таллинский парк'!B61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
+        <f>SUM('Астрид'!B62,'Курортный'!B62,'Новое Колпино'!B62,'Таллинский парк'!B62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
+        <f>SUM('Астрид'!B63,'Курортный'!B63,'Новое Колпино'!B63,'Таллинский парк'!B63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
+        <f>SUM('Астрид'!B64,'Курортный'!B64,'Новое Колпино'!B64,'Таллинский парк'!B64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
+        <f>SUM('Астрид'!B65,'Курортный'!B65,'Новое Колпино'!B65,'Таллинский парк'!B65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
+        <f>SUM('Астрид'!B66,'Курортный'!B66,'Новое Колпино'!B66,'Таллинский парк'!B66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
+        <f>SUM('Астрид'!B67,'Курортный'!B67,'Новое Колпино'!B67,'Таллинский парк'!B67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
+        <f>SUM('Астрид'!B68,'Курортный'!B68,'Новое Колпино'!B68,'Таллинский парк'!B68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
+        <f>SUM('Астрид'!B69,'Курортный'!B69,'Новое Колпино'!B69,'Таллинский парк'!B69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
+        <f>SUM('Астрид'!B70,'Курортный'!B70,'Новое Колпино'!B70,'Таллинский парк'!B70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
+        <f>SUM('Астрид'!B71,'Курортный'!B71,'Новое Колпино'!B71,'Таллинский парк'!B71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
+        <f>SUM('Астрид'!B72,'Курортный'!B72,'Новое Колпино'!B72,'Таллинский парк'!B72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
+        <f>SUM('Астрид'!B73,'Курортный'!B73,'Новое Колпино'!B73,'Таллинский парк'!B73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
+        <f>SUM('Астрид'!B74,'Курортный'!B74,'Новое Колпино'!B74,'Таллинский парк'!B74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
+        <f>SUM('Астрид'!B75,'Курортный'!B75,'Новое Колпино'!B75,'Таллинский парк'!B75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
+        <f>SUM('Астрид'!B76,'Курортный'!B76,'Новое Колпино'!B76,'Таллинский парк'!B76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
+        <f>SUM('Астрид'!B77,'Курортный'!B77,'Новое Колпино'!B77,'Таллинский парк'!B77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
+        <f>SUM('Астрид'!B78,'Курортный'!B78,'Новое Колпино'!B78,'Таллинский парк'!B78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
+        <f>SUM('Астрид'!B79,'Курортный'!B79,'Новое Колпино'!B79,'Таллинский парк'!B79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
+        <f>SUM('Астрид'!B83,'Курортный'!B83,'Новое Колпино'!B83,'Таллинский парк'!B83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
+        <f>SUM('Астрид'!B84,'Курортный'!B84,'Новое Колпино'!B84,'Таллинский парк'!B84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
+        <f>SUM('Астрид'!B85,'Курортный'!B85,'Новое Колпино'!B85,'Таллинский парк'!B85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
+        <f>SUM('Астрид'!B86,'Курортный'!B86,'Новое Колпино'!B86,'Таллинский парк'!B86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
+        <f>SUM('Астрид'!B88,'Курортный'!B88,'Новое Колпино'!B88,'Таллинский парк'!B88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
+        <f>SUM('Астрид'!B92,'Курортный'!B92,'Новое Колпино'!B92,'Таллинский парк'!B92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
+        <f>SUM('Астрид'!B93,'Курортный'!B93,'Новое Колпино'!B93,'Таллинский парк'!B93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
+        <f>SUM('Астрид'!B94,'Курортный'!B94,'Новое Колпино'!B94,'Таллинский парк'!B94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
+        <f>SUM('Астрид'!B96,'Курортный'!B96,'Новое Колпино'!B96,'Таллинский парк'!B96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
+        <f>SUM('Астрид'!B97,'Курортный'!B97,'Новое Колпино'!B97,'Таллинский парк'!B97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5711,9 +5711,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>2234662.3</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -5762,9 +5761,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5819,9 +5819,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>2234662.3</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -5870,9 +5869,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>1764662.3</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>228370.58</v>
@@ -5919,9 +5917,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="n">
+        <v>470000</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5974,9 +5971,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -6031,9 +6029,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>2591097.77</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -6082,9 +6079,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6139,9 +6137,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -6196,9 +6195,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>62763.75999999999</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -6247,9 +6245,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6304,9 +6303,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -6361,9 +6361,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -6418,9 +6419,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>52763.75999999999</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>10587.92</v>
@@ -6467,9 +6467,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>10000</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -6520,9 +6519,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6577,9 +6577,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6634,9 +6635,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>839437.0600000001</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>209688.53</v>
@@ -6683,9 +6683,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>1104988.18</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>294494.09</v>
@@ -6732,9 +6731,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>145177</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>19188.5</v>
@@ -6781,9 +6779,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>31773.77</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>13380.59</v>
@@ -6832,9 +6829,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -6889,9 +6887,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6946,9 +6945,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -7003,9 +7003,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -7060,9 +7061,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7117,9 +7119,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>2038</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>1019</v>
@@ -7170,9 +7171,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7227,9 +7229,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7284,9 +7287,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7341,9 +7345,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>404920</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -7392,9 +7395,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>30000</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>10000</v>
@@ -7441,9 +7443,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>240000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>60000</v>
@@ -7490,9 +7491,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>6000</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -7539,9 +7539,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7596,9 +7597,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>126920</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>26500</v>
@@ -7645,9 +7645,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7702,9 +7703,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>2000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -7755,9 +7755,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7812,9 +7813,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>-356435.4700000002</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -7863,9 +7863,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>-15.95%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -7914,9 +7915,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>281480.82</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -7965,9 +7965,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>281480.82</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>55821.21</v>
@@ -8014,9 +8013,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -8071,9 +8071,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -8122,9 +8123,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8179,9 +8181,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8236,9 +8239,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8293,9 +8297,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -8344,9 +8349,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8401,9 +8407,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8458,9 +8465,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8515,9 +8523,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8572,9 +8581,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8629,9 +8639,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8686,9 +8697,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8743,9 +8755,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -8794,9 +8807,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8851,9 +8865,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8908,9 +8923,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -8965,9 +8981,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -9022,9 +9039,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -9079,9 +9097,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9136,9 +9155,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9193,9 +9213,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9250,9 +9271,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9307,9 +9329,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9364,9 +9387,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9421,9 +9445,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9478,9 +9503,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9535,9 +9561,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9592,9 +9619,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9649,9 +9677,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9706,9 +9735,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9763,9 +9793,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9820,9 +9851,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9877,9 +9909,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>-637916.2900000003</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -9928,9 +9959,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>-28.55%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -9979,9 +10011,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -10030,9 +10063,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -10087,9 +10121,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10144,9 +10179,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10201,9 +10237,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10258,9 +10295,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -10309,9 +10347,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10366,9 +10405,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>-637916.2900000003</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -10417,9 +10455,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>-28.55%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -10468,9 +10507,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -10519,9 +10559,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10576,9 +10617,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10633,9 +10675,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10690,9 +10733,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>159639.28</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -10741,9 +10783,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
@@ -10794,9 +10835,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>139639.28</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>38678.65</v>
@@ -10843,9 +10883,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>-797555.5700000003</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -10894,9 +10933,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>-35.69%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -11104,9 +11144,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>7953554.7</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -11155,9 +11194,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11212,9 +11252,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>7953554.7</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -11263,9 +11302,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>5197391.32</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1299347.83</v>
@@ -11312,9 +11350,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="n">
+        <v>2756163.38</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>772382</v>
@@ -11361,9 +11398,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11418,9 +11456,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>6625547.439999999</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -11469,9 +11506,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11526,9 +11564,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11583,9 +11622,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>62999</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -11634,9 +11672,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11691,9 +11730,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11748,9 +11788,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11805,9 +11846,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>40000</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>10000</v>
@@ -11854,9 +11894,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>22999</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>7999</v>
@@ -11903,9 +11942,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -11960,9 +12000,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -12017,9 +12058,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>2690034.97</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>695034.97</v>
@@ -12066,9 +12106,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>2400000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>600000</v>
@@ -12115,9 +12154,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>299800</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>60061</v>
@@ -12164,9 +12202,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>112000</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>28000</v>
@@ -12213,9 +12250,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12270,9 +12308,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12327,9 +12366,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -12384,9 +12424,8 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="n">
+        <v>7069</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>7069</v>
@@ -12439,9 +12478,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12496,9 +12536,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -12545,9 +12584,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12602,9 +12642,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12659,9 +12700,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12716,9 +12758,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>1041644.47</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -12767,9 +12808,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>10000</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>2500</v>
@@ -12816,9 +12856,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>440000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>110000</v>
@@ -12865,9 +12904,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>14004.04</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>3504.04</v>
@@ -12914,9 +12952,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -12971,9 +13010,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>382200</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>95550</v>
@@ -13020,9 +13058,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -13077,9 +13116,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>16000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>4000</v>
@@ -13126,9 +13164,8 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="n">
+        <v>179440.43</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>44440.43</v>
@@ -13175,9 +13212,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>1328007.260000001</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -13226,9 +13262,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>16.70%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -13277,9 +13314,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>556192.48</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -13328,9 +13364,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>556192.48</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>139048.12</v>
@@ -13377,9 +13412,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13434,9 +13470,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -13485,9 +13522,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13542,9 +13580,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13599,9 +13638,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13656,9 +13696,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -13707,9 +13748,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13764,9 +13806,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13821,9 +13864,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -13878,9 +13922,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -13935,9 +13980,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -13992,9 +14038,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -14049,9 +14096,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14106,9 +14154,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -14157,9 +14206,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14214,9 +14264,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14271,9 +14322,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14328,9 +14380,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14385,9 +14438,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14442,9 +14496,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14499,9 +14554,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14556,9 +14612,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14613,9 +14670,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14670,9 +14728,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14727,9 +14786,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14784,9 +14844,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14841,9 +14902,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -14898,9 +14960,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -14955,9 +15018,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -15012,9 +15076,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -15069,9 +15134,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15126,9 +15192,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15183,9 +15250,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15240,9 +15308,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>771814.7800000007</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -15291,9 +15358,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>9.70%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -15342,9 +15410,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -15393,9 +15462,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15450,9 +15520,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15507,9 +15578,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15564,9 +15636,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15621,9 +15694,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -15672,9 +15746,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15729,9 +15804,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>771814.7800000007</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -15780,9 +15854,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>9.70%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -15831,9 +15906,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -15882,9 +15958,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -15939,9 +16016,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -15996,9 +16074,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16053,9 +16132,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>490361.28</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -16104,9 +16182,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>112000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>28000</v>
@@ -16153,9 +16230,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>378361.28</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>94590.32000000001</v>
@@ -16202,9 +16278,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>281453.5000000007</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -16253,9 +16328,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -16463,9 +16539,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>10175223.66</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -16514,9 +16589,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16571,9 +16647,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>10175223.66</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -16622,9 +16697,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>10175223.66</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>2759091.96</v>
@@ -16671,9 +16745,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16728,9 +16803,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16785,9 +16861,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>8684016.199999999</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -16836,9 +16911,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -16893,9 +16969,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -16950,9 +17027,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>601711.53</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -17001,9 +17077,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -17058,9 +17135,8 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="n">
+        <v>352000</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>88000</v>
@@ -17107,9 +17183,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17164,9 +17241,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>133810.13</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>43810.13</v>
@@ -17213,9 +17289,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>85901.39999999999</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>5901.4</v>
@@ -17262,9 +17337,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17319,9 +17395,8 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="n">
+        <v>30000</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -17374,9 +17449,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>2740000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>685000</v>
@@ -17423,9 +17497,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>3718084.67</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>958084.67</v>
@@ -17472,9 +17545,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>112000</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>28000</v>
@@ -17521,9 +17593,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>574820</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>143705</v>
@@ -17570,9 +17641,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -17627,9 +17699,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17684,9 +17757,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17741,9 +17815,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17798,9 +17873,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -17855,9 +17931,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -17904,9 +17979,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -17961,9 +18037,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -18018,9 +18095,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18075,9 +18153,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>925400</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -18126,9 +18203,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>5000</v>
@@ -18175,9 +18251,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>400000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>100000</v>
@@ -18224,9 +18299,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>5000</v>
@@ -18273,9 +18347,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18330,9 +18405,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>477400</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>119350</v>
@@ -18379,9 +18453,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18436,9 +18511,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -18485,9 +18559,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18542,9 +18617,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>1491207.460000001</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -18593,9 +18667,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>14.66%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -18644,9 +18719,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>1194777.16</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -18695,9 +18769,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>1182777.16</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>295694.29</v>
@@ -18744,9 +18817,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18801,9 +18875,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -18852,9 +18927,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -18909,9 +18985,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -18966,9 +19043,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -19023,9 +19101,8 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -19074,9 +19151,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -19131,9 +19209,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19188,9 +19267,8 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C55" s="7" t="n">
         <v>3000</v>
@@ -19237,9 +19315,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -19294,9 +19373,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19351,9 +19431,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19408,9 +19489,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19465,9 +19547,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -19516,9 +19599,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19573,9 +19657,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19630,9 +19715,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19687,9 +19773,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19744,9 +19831,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19801,9 +19889,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -19858,9 +19947,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -19915,9 +20005,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -19972,9 +20063,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -20029,9 +20121,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20086,9 +20179,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20143,9 +20237,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20200,9 +20295,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20257,9 +20353,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20314,9 +20411,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20371,9 +20469,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20428,9 +20527,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20485,9 +20585,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20542,9 +20643,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20599,9 +20701,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>296430.300000001</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -20650,9 +20751,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>2.91%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -20701,9 +20803,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -20752,9 +20855,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -20809,9 +20913,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -20866,9 +20971,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -20923,9 +21029,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -20980,9 +21087,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -21031,9 +21139,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21088,9 +21197,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>296430.300000001</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -21139,9 +21247,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>2.91%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -21190,9 +21299,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -21241,9 +21351,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21298,9 +21409,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21355,9 +21467,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21412,9 +21525,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>638865.48</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -21463,9 +21575,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>168000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>42000</v>
@@ -21512,9 +21623,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>470865.48</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>117716.37</v>
@@ -21561,9 +21671,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>-342435.179999999</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -21612,9 +21721,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>-3.37%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -21822,9 +21932,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>6397856.92</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -21873,9 +21982,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -21930,9 +22040,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>6397856.92</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -21981,9 +22090,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>6397856.92</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1599464.23</v>
@@ -22030,9 +22138,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22087,9 +22196,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22144,9 +22254,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>3517036.57</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -22195,9 +22304,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22252,9 +22362,8 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="n">
+        <v>15000</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>15000</v>
@@ -22307,9 +22416,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>75906</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -22358,9 +22466,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22415,9 +22524,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22472,9 +22582,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22529,9 +22640,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>9525</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>525</v>
@@ -22578,9 +22688,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>48381</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>33381</v>
@@ -22627,9 +22736,8 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="n">
+        <v>18000</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>18000</v>
@@ -22682,9 +22790,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22739,9 +22848,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>1056000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>264000</v>
@@ -22788,9 +22896,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>1582778</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>532778</v>
@@ -22837,9 +22944,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>53052.57</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>11052.57</v>
@@ -22886,9 +22992,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -22943,9 +23050,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -23000,9 +23108,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -23057,9 +23166,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23114,9 +23224,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23171,9 +23282,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23228,9 +23340,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -23285,9 +23398,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -23342,9 +23456,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23399,9 +23514,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23456,9 +23572,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>734300</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -23507,9 +23622,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>32500</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>12500</v>
@@ -23556,9 +23670,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>480000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>120000</v>
@@ -23605,9 +23718,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -23654,9 +23766,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23711,9 +23824,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>205800</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>51450</v>
@@ -23760,9 +23872,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -23817,9 +23930,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -23866,9 +23978,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -23923,9 +24036,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>2880820.35</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -23974,9 +24086,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>45.03%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -24025,9 +24138,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>394222.48</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -24076,9 +24188,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>394222.48</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>98555.62</v>
@@ -24125,9 +24236,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24182,9 +24294,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -24233,9 +24346,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24290,9 +24404,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24347,9 +24462,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24404,9 +24520,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -24455,9 +24572,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24512,9 +24630,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24569,9 +24688,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24626,9 +24746,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24683,9 +24804,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24740,9 +24862,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -24797,9 +24920,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -24854,9 +24978,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -24905,9 +25030,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -24962,9 +25088,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -25019,9 +25146,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25076,9 +25204,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25133,9 +25262,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25190,9 +25320,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25247,9 +25378,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25304,9 +25436,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25361,9 +25494,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25418,9 +25552,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25475,9 +25610,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25532,9 +25668,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25589,9 +25726,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25646,9 +25784,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25703,9 +25842,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -25760,9 +25900,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -25817,9 +25958,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -25874,9 +26016,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -25931,9 +26074,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -25988,9 +26132,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>2486597.87</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -26039,9 +26182,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>38.87%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -26090,9 +26234,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -26141,9 +26286,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26198,9 +26344,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26255,9 +26402,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26312,9 +26460,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26369,9 +26518,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -26420,9 +26570,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26477,9 +26628,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>2486597.87</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -26528,9 +26678,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>38.87%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -26579,9 +26730,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -26630,9 +26782,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26687,9 +26840,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -26744,9 +26898,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -26801,9 +26956,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>400659.92</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -26852,9 +27006,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>96000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>24000</v>
@@ -26901,9 +27054,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>304659.92</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>76164.98</v>
@@ -26950,9 +27102,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>2085937.95</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -27001,9 +27152,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>32.60%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
